--- a/eval/gold_scenarios/workpapers/q1_exception_dc9_signoff_missing_01/billing_calc.xlsx
+++ b/eval/gold_scenarios/workpapers/q1_exception_dc9_signoff_missing_01/billing_calc.xlsx
@@ -431,7 +431,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Epsilon Holdings</t>
+          <t>Delta Sub-Fund</t>
         </is>
       </c>
     </row>
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>482463265</v>
+        <v>28116303</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4824632</v>
+        <v>70290</v>
       </c>
     </row>
     <row r="7">
@@ -487,7 +487,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>SY</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-02-28</t>
         </is>
       </c>
     </row>
